--- a/test-fixtures/e2e/İşçilik_Hangar Yangın Keşif Özeti_R02 (1).xlsx
+++ b/test-fixtures/e2e/İşçilik_Hangar Yangın Keşif Özeti_R02 (1).xlsx
@@ -47,7 +47,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="65">
   <si>
-    <t>BEARO HAVACİLİK 1 NOLU HANGAR ve OFİS PROJESİ HANGAR BÖLÜMÜ MEKANİK TESİSAT KEŞİF ÖZETİ</t>
+    <t>FIRMA-J HAVACİLİK 1 NOLU HANGAR ve OFİS PROJESİ HANGAR BÖLÜMÜ MEKANİK TESİSAT KEŞİF ÖZETİ</t>
   </si>
   <si>
     <t xml:space="preserve">YANGIN TESİSAT İŞLERİ  </t>
